--- a/ExportOrderWebServer/Resources/TemplateFillBill.xlsx
+++ b/ExportOrderWebServer/Resources/TemplateFillBill.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26924"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF6528E-E32B-4B81-AD91-C87A2F57767D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAB8FC8-A3DA-45F6-9284-C818C476BB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="601" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -248,9 +248,11 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -585,7 +587,6 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="14"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -610,7 +611,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="15"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -622,7 +623,6 @@
       <c r="L2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="14"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -637,7 +637,7 @@
         <v>30</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="16"/>
+      <c r="E3" s="15"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -660,7 +660,6 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="14"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -683,7 +682,6 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="14"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -757,7 +755,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="6"/>
